--- a/Doo-Doc/Nueva Version Victus/MuestreoDatos/Agenda Muestreo Datos.xlsx
+++ b/Doo-Doc/Nueva Version Victus/MuestreoDatos/Agenda Muestreo Datos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\DOO 2024 BD\DOO\victus-doc\Doo-Doc\Nueva Version Victus\MuestreoDatos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C1BFA9-9677-42BB-A2B3-276620FEC457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5887841-55C1-463E-9ED8-41A298A523D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16695" yWindow="4440" windowWidth="16800" windowHeight="14190" activeTab="3" xr2:uid="{2D4B8DA6-DD27-486A-88C5-FC69C929F1D2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{2D4B8DA6-DD27-486A-88C5-FC69C929F1D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Objetos de dominio" sheetId="1" r:id="rId1"/>
@@ -744,8 +744,8 @@
       <sheetName val="ZonaComun"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
       <sheetData sheetId="2">
         <row r="4">
           <cell r="I4" t="str">
@@ -773,9 +773,9 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1099,13 +1099,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ADC7617-6509-431F-A99E-8882BF74D5E4}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.7109375" customWidth="1"/>
-    <col min="2" max="2" width="58.28515625" customWidth="1"/>
+    <col min="1" max="1" width="27.6640625" customWidth="1"/>
+    <col min="2" max="2" width="58.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1113,7 +1113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1129,7 +1129,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -1150,19 +1150,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AAB45A7-2401-4156-812B-1376902CA2CF}">
   <dimension ref="A1:J15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.7109375" customWidth="1"/>
-    <col min="3" max="3" width="24.7109375" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" customWidth="1"/>
+    <col min="3" max="3" width="24.6640625" customWidth="1"/>
     <col min="4" max="4" width="27" customWidth="1"/>
-    <col min="5" max="7" width="21.7109375" customWidth="1"/>
-    <col min="8" max="8" width="20.28515625" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" customWidth="1"/>
-    <col min="10" max="10" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.5703125" customWidth="1"/>
+    <col min="5" max="7" width="21.6640625" customWidth="1"/>
+    <col min="8" max="8" width="20.33203125" customWidth="1"/>
+    <col min="9" max="9" width="23.6640625" customWidth="1"/>
+    <col min="10" max="10" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>6</v>
       </c>
@@ -1176,7 +1176,7 @@
       <c r="I1" s="5"/>
       <c r="J1" s="5"/>
     </row>
-    <row r="2" spans="1:10" s="35" customFormat="1" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" s="35" customFormat="1" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="34" t="s">
         <v>25</v>
       </c>
@@ -1208,7 +1208,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -1240,7 +1240,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="25">
         <v>1</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>Piscina-Forest apartamentos</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="28">
         <v>2</v>
       </c>
@@ -1308,7 +1308,7 @@
         <v>Gimnasio-Forest apartamentos</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="28">
         <v>3</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>piscinaAdultos-Natural</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A7" s="28">
         <v>4</v>
       </c>
@@ -1376,7 +1376,7 @@
         <v>Salón de Eventos-Riogrande</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A8" s="28">
         <v>5</v>
       </c>
@@ -1410,7 +1410,7 @@
         <v>Cancha de Fútbol-Bolivar</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A9" s="28">
         <v>6</v>
       </c>
@@ -1444,7 +1444,7 @@
         <v>Piscina Pequeña-Natural</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10" s="28">
         <v>7</v>
       </c>
@@ -1478,7 +1478,7 @@
         <v>Zona BBQ-Ventus</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A11" s="28">
         <v>8</v>
       </c>
@@ -1512,7 +1512,7 @@
         <v>Cancha de Tenis-Riogrande</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A12" s="28">
         <v>9</v>
       </c>
@@ -1546,18 +1546,18 @@
         <v>Sala de Juegos-Forest apartamentos</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B13" s="30"/>
       <c r="C13" s="31"/>
       <c r="D13" s="32"/>
       <c r="H13" s="32"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C14" s="31"/>
       <c r="D14" s="32"/>
       <c r="H14" s="32"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C15" s="31"/>
       <c r="D15" s="32"/>
       <c r="H15" s="32"/>
@@ -1579,17 +1579,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4578BD62-C112-42DC-9A20-08C85087F0AF}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="40.42578125" customWidth="1"/>
-    <col min="3" max="3" width="40.5703125" customWidth="1"/>
-    <col min="4" max="4" width="17.28515625" customWidth="1"/>
-    <col min="5" max="5" width="46.140625" customWidth="1"/>
-    <col min="6" max="6" width="44.7109375" customWidth="1"/>
-    <col min="7" max="7" width="98.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.44140625" customWidth="1"/>
+    <col min="3" max="3" width="40.5546875" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" customWidth="1"/>
+    <col min="5" max="5" width="46.109375" customWidth="1"/>
+    <col min="6" max="6" width="44.6640625" customWidth="1"/>
+    <col min="7" max="7" width="98.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="68" t="s">
         <v>6</v>
       </c>
@@ -1599,7 +1599,7 @@
       <c r="E1" s="68"/>
       <c r="F1" s="5"/>
     </row>
-    <row r="2" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="69" x14ac:dyDescent="0.3">
       <c r="A2" s="34" t="s">
         <v>7</v>
       </c>
@@ -1622,7 +1622,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -1645,7 +1645,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="36">
         <v>1</v>
       </c>
@@ -1670,7 +1670,7 @@
         <v xml:space="preserve">Piscina-Forest apartamentos - 18  septiembre 2024 6:00:00 a. m.  hasta - 18  septiembre 2024 2:00:00 p. m. </v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="36">
         <v>2</v>
       </c>
@@ -1695,7 +1695,7 @@
         <v xml:space="preserve">Piscina-Forest apartamentos - 18  septiembre 2024 3:00:00 p. m.  hasta - 18  septiembre 2024 9:00:00 p. m. </v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>3</v>
       </c>
@@ -1720,7 +1720,7 @@
         <v xml:space="preserve">Gimnasio-Forest apartamentos - 18  septiembre 2024 6:00:00 a. m.  hasta - 18  septiembre 2024 2:00:00 p. m. </v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="39">
         <v>4</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v xml:space="preserve">Gimnasio-Forest apartamentos - 18  septiembre 2024 3:00:00 p. m.  hasta - 18  septiembre 2024 9:00:00 p. m. </v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="42">
         <v>5</v>
       </c>
@@ -1770,7 +1770,7 @@
         <v xml:space="preserve">piscinaAdultos-Natural - 20  septiembre 2024 10:00:00 a. m.  hasta - 20  septiembre 2024 1:00:00 p. m. </v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="45">
         <v>6</v>
       </c>
@@ -1795,7 +1795,7 @@
         <v xml:space="preserve">Salón de Eventos-Riogrande - 18  septiembre 2024 8:00:00 a. m.  hasta - 18  septiembre 2024 12:00:00 p. m. </v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="48">
         <v>7</v>
       </c>
@@ -1820,7 +1820,7 @@
         <v xml:space="preserve">Cancha de Fútbol-Bolivar - 18  septiembre 2024 8:00:00 a. m.  hasta - 18  septiembre 2024 12:00:00 p. m. </v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="51">
         <v>8</v>
       </c>
@@ -1845,7 +1845,7 @@
         <v xml:space="preserve">Piscina Pequeña-Natural - 20  septiembre 2024 8:00:00 a. m.  hasta - 20  septiembre 2024 12:00:00 p. m. </v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="54">
         <v>9</v>
       </c>
@@ -1870,7 +1870,7 @@
         <v xml:space="preserve">Zona BBQ-Ventus - 20  septiembre 2024 8:00:00 a. m.  hasta - 20  septiembre 2024 12:00:00 p. m. </v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="58">
         <v>10</v>
       </c>
@@ -1895,7 +1895,7 @@
         <v xml:space="preserve">Cancha de Tenis-Riogrande - 22  septiembre 2024 8:00:00 a. m.  hasta - 22  septiembre 2024 12:00:00 p. m. </v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="33"/>
     </row>
   </sheetData>
@@ -1923,17 +1923,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1481DBD8-8614-460B-A4B3-0BC96282F835}">
   <dimension ref="A1:G30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.140625" customWidth="1"/>
+    <col min="1" max="1" width="14.109375" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
-    <col min="6" max="6" width="133.7109375" customWidth="1"/>
-    <col min="7" max="7" width="140.7109375" customWidth="1"/>
+    <col min="3" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="6" max="6" width="133.6640625" customWidth="1"/>
+    <col min="7" max="7" width="140.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="68" t="s">
         <v>6</v>
       </c>
@@ -1943,7 +1943,7 @@
       <c r="E1" s="68"/>
       <c r="F1" s="5"/>
     </row>
-    <row r="2" spans="1:7" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A2" s="34" t="s">
         <v>16</v>
       </c>
@@ -1966,7 +1966,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -1989,7 +1989,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>1</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v xml:space="preserve">Turno 1-Piscina-Forest apartamentos - 18  septiembre 2024 6:00:00 a. m.  hasta - 18  septiembre 2024 2:00:00 p. m. - 6:00:00 a. m. - 8:00:00 a. m. </v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>2</v>
       </c>
@@ -2037,7 +2037,7 @@
         <v xml:space="preserve">Turno 2-Piscina-Forest apartamentos - 18  septiembre 2024 6:00:00 a. m.  hasta - 18  septiembre 2024 2:00:00 p. m. - 8:00:00 a. m. - 10:00:00 a. m. </v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>3</v>
       </c>
@@ -2061,7 +2061,7 @@
         <v xml:space="preserve">Turno 3-Piscina-Forest apartamentos - 18  septiembre 2024 6:00:00 a. m.  hasta - 18  septiembre 2024 2:00:00 p. m. - 10:00:00 a. m. - 12:00:00 p. m. </v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>4</v>
       </c>
@@ -2085,7 +2085,7 @@
         <v xml:space="preserve">Turno 4-Piscina-Forest apartamentos - 18  septiembre 2024 6:00:00 a. m.  hasta - 18  septiembre 2024 2:00:00 p. m. - 1:00:00 p. m. - 2:00:00 p. m. </v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
         <v>5</v>
       </c>
@@ -2109,7 +2109,7 @@
         <v xml:space="preserve">Turno 1-Gimnasio-Forest apartamentos - 18  septiembre 2024 3:00:00 p. m.  hasta - 18  septiembre 2024 9:00:00 p. m. - 3:00:00 p. m. - 5:00:00 p. m. </v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
         <v>6</v>
       </c>
@@ -2133,7 +2133,7 @@
         <v xml:space="preserve">Turno 2-Gimnasio-Forest apartamentos - 18  septiembre 2024 3:00:00 p. m.  hasta - 18  septiembre 2024 9:00:00 p. m. - 5:00:00 p. m. - 7:00:00 p. m. </v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
         <v>7</v>
       </c>
@@ -2157,7 +2157,7 @@
         <v xml:space="preserve">Turno 3-Gimnasio-Forest apartamentos - 18  septiembre 2024 3:00:00 p. m.  hasta - 18  septiembre 2024 9:00:00 p. m. - 7:00:00 p. m. - 9:00:00 p. m. </v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="14">
         <v>8</v>
       </c>
@@ -2181,7 +2181,7 @@
         <v xml:space="preserve">Turno 1-piscinaAdultos-Natural - 20  septiembre 2024 10:00:00 a. m.  hasta - 20  septiembre 2024 1:00:00 p. m. - 10:00:00 p. m. - 11:00:00 p. m. </v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="14">
         <v>9</v>
       </c>
@@ -2205,7 +2205,7 @@
         <v xml:space="preserve">Turno 2-piscinaAdultos-Natural - 20  septiembre 2024 10:00:00 a. m.  hasta - 20  septiembre 2024 1:00:00 p. m. - 11:00:00 a. m. - 12:00:00 p. m. </v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="14">
         <v>10</v>
       </c>
@@ -2229,7 +2229,7 @@
         <v xml:space="preserve">Turno 3-piscinaAdultos-Natural - 20  septiembre 2024 10:00:00 a. m.  hasta - 20  septiembre 2024 1:00:00 p. m. - 12:00:00 p. m. - 1:00:00 p. m. </v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="17">
         <v>11</v>
       </c>
@@ -2253,7 +2253,7 @@
         <v xml:space="preserve">Turno 1-Salón de Eventos-Riogrande - 18  septiembre 2024 8:00:00 a. m.  hasta - 18  septiembre 2024 12:00:00 p. m. - 8:00:00 a. m. - 9:00:00 a. m. </v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="17">
         <v>12</v>
       </c>
@@ -2277,7 +2277,7 @@
         <v xml:space="preserve">Turno 2-Salón de Eventos-Riogrande - 18  septiembre 2024 8:00:00 a. m.  hasta - 18  septiembre 2024 12:00:00 p. m. - 9:00:00 a. m. - 10:00:00 a. m. </v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="17">
         <v>13</v>
       </c>
@@ -2301,7 +2301,7 @@
         <v xml:space="preserve">Turno 3-Salón de Eventos-Riogrande - 18  septiembre 2024 8:00:00 a. m.  hasta - 18  septiembre 2024 12:00:00 p. m. - 10:00:00 a. m. - 11:00:00 a. m. </v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="17">
         <v>14</v>
       </c>
@@ -2325,7 +2325,7 @@
         <v xml:space="preserve">Turno 4-Salón de Eventos-Riogrande - 18  septiembre 2024 8:00:00 a. m.  hasta - 18  septiembre 2024 12:00:00 p. m. - 11:00:00 a. m. - 12:00:00 p. m. </v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="65">
         <v>15</v>
       </c>
@@ -2349,7 +2349,7 @@
         <v xml:space="preserve">Turno 1-Cancha de Fútbol-Bolivar - 18  septiembre 2024 8:00:00 a. m.  hasta - 18  septiembre 2024 12:00:00 p. m. - 8:00:00 a. m. - 9:00:00 a. m. </v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="65">
         <v>16</v>
       </c>
@@ -2373,7 +2373,7 @@
         <v xml:space="preserve">Turno 2-Cancha de Fútbol-Bolivar - 18  septiembre 2024 8:00:00 a. m.  hasta - 18  septiembre 2024 12:00:00 p. m. - 9:00:00 a. m. - 10:00:00 a. m. </v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="65">
         <v>17</v>
       </c>
@@ -2397,7 +2397,7 @@
         <v xml:space="preserve">Turno 3-Cancha de Fútbol-Bolivar - 18  septiembre 2024 8:00:00 a. m.  hasta - 18  septiembre 2024 12:00:00 p. m. - 10:00:00 a. m. - 11:00:00 a. m. </v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="65">
         <v>18</v>
       </c>
@@ -2421,7 +2421,7 @@
         <v xml:space="preserve">Turno 4-Cancha de Fútbol-Bolivar - 18  septiembre 2024 8:00:00 a. m.  hasta - 18  septiembre 2024 12:00:00 p. m. - 11:00:00 a. m. - 12:00:00 p. m. </v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="17">
         <v>19</v>
       </c>
@@ -2435,7 +2435,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="17">
         <v>20</v>
       </c>
@@ -2449,7 +2449,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="17">
         <v>21</v>
       </c>
@@ -2463,7 +2463,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="17">
         <v>22</v>
       </c>
@@ -2477,7 +2477,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="17">
         <v>23</v>
       </c>
@@ -2491,7 +2491,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="17">
         <v>24</v>
       </c>
@@ -2505,7 +2505,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="17">
         <v>25</v>
       </c>
@@ -2515,10 +2515,10 @@
       <c r="E28" s="64"/>
       <c r="F28" s="64"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F29" s="62"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F30" s="62"/>
     </row>
   </sheetData>

--- a/Doo-Doc/Nueva Version Victus/MuestreoDatos/Agenda Muestreo Datos.xlsx
+++ b/Doo-Doc/Nueva Version Victus/MuestreoDatos/Agenda Muestreo Datos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\DOO 2024 BD\DOO\victus-doc\Doo-Doc\Nueva Version Victus\MuestreoDatos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5887841-55C1-463E-9ED8-41A298A523D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECC33A31-D97B-4683-AC4C-DB498345BB62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{2D4B8DA6-DD27-486A-88C5-FC69C929F1D2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{2D4B8DA6-DD27-486A-88C5-FC69C929F1D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Objetos de dominio" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,6 @@
     <sheet name="Agenda" sheetId="2" r:id="rId3"/>
     <sheet name="Turno" sheetId="3" r:id="rId4"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId5"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -42,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="102">
   <si>
     <t>Nombre</t>
   </si>
@@ -50,9 +47,6 @@
     <t>Descripción</t>
   </si>
   <si>
-    <t>ConjuntoResidencial</t>
-  </si>
-  <si>
     <t>ZonaComun</t>
   </si>
   <si>
@@ -131,12 +125,6 @@
     <t>Es un dato que representa el número de personas que admite una zona común.</t>
   </si>
   <si>
-    <t>Es un dato que representa el texto de normas que puede tener la zona común</t>
-  </si>
-  <si>
-    <t>Es un dato que representa el conjunto residencial al cual pertenece la zona común.</t>
-  </si>
-  <si>
     <t>No es posible tener más de una zona común con el mismo nombre para un mismo conjunto residencial.</t>
   </si>
   <si>
@@ -149,111 +137,51 @@
     <t>Es un espacio deportivo y lúdico</t>
   </si>
   <si>
-    <t>Para reservar la psicina debe contar con 1 dia de anterioridad</t>
-  </si>
-  <si>
     <t>Gimnasio</t>
   </si>
   <si>
     <t>Espacio que cuenta con diferentes maquinas para la ejercitación</t>
   </si>
   <si>
-    <t>Usar la maquinaria con toalla y mantener la higiene</t>
-  </si>
-  <si>
     <t>piscinaAdultos</t>
   </si>
   <si>
-    <t>Minutos</t>
-  </si>
-  <si>
-    <t>Hora</t>
-  </si>
-  <si>
-    <t>piscina001.jpg</t>
-  </si>
-  <si>
-    <t>gimnasio002.jpg</t>
-  </si>
-  <si>
-    <t>piscinaadultos003.jpg</t>
-  </si>
-  <si>
     <t>Salón de Eventos</t>
   </si>
   <si>
-    <t>salón de eventos004.jpg</t>
-  </si>
-  <si>
     <t>Un espacio amplio para celebrar reuniones sociales y familiares.</t>
   </si>
   <si>
-    <t>Reservar con al menos 3 días de anticipación. No se permite el uso de pirotecnia.</t>
-  </si>
-  <si>
     <t>Cancha de Fútbol</t>
   </si>
   <si>
-    <t>cancha de fútbol005.jpg</t>
-  </si>
-  <si>
     <t>Cancha de césped sintético para actividades deportivas en equipo.</t>
   </si>
   <si>
-    <t>Se requiere reservar con 2 horas de anticipación. Uso exclusivo de zapatos con tacos adecuados.</t>
-  </si>
-  <si>
     <t>Piscina Pequeña</t>
   </si>
   <si>
-    <t>piscina pequeña006.jpg</t>
-  </si>
-  <si>
     <t>Piscina diseñada para niños, con profundidades seguras y vigilancia.</t>
   </si>
   <si>
-    <t>Es necesario el acompañamiento de un adulto. No se permite correr alrededor de la piscina.</t>
-  </si>
-  <si>
     <t>Zona BBQ</t>
   </si>
   <si>
-    <t>zona bbq007.jpg</t>
-  </si>
-  <si>
     <t>Área equipada con parrillas y mesas para realizar asados al aire libre.</t>
   </si>
   <si>
-    <t>Limpiar el área después de cada uso. Se debe reservar con 1 día de anticipación.</t>
-  </si>
-  <si>
     <t>Cancha de Tenis</t>
   </si>
   <si>
-    <t>cancha de tenis008.jpg</t>
-  </si>
-  <si>
     <t>Espacio deportivo para la práctica de tenis en un ambiente profesional</t>
   </si>
   <si>
-    <t>Uso exclusivo de zapatos de suela lisa. Reservar con 4 horas de anticipación.</t>
-  </si>
-  <si>
     <t>Sala de Juegos</t>
   </si>
   <si>
-    <t>sala de juegos009.jpg</t>
-  </si>
-  <si>
     <t>Sala equipada con mesas de ping-pong, billar y juegos de mesa para el disfrute familiar.</t>
   </si>
   <si>
-    <t>Reservar con al menos 2 horas de anticipación. Prohibido el consumo de alimentos en la sala.</t>
-  </si>
-  <si>
-    <t>Este atributo hace referencia a la imagen que va a acompañar a la zona común para mayor facilidad a la hora de identificarlo.</t>
-  </si>
-  <si>
     <t>Este es un dato tipo texto que representa el nombre de como se llama la agenda que se esta programando</t>
   </si>
   <si>
@@ -278,30 +206,9 @@
     <t>horaInicio</t>
   </si>
   <si>
-    <t>imagen</t>
-  </si>
-  <si>
-    <t>normas</t>
-  </si>
-  <si>
-    <t>Este es le dato que representa el tiempo de uso por numero entero de un residente</t>
-  </si>
-  <si>
     <t>Es un dato que representa la unidad de tiempo de uso de una zona comun para un residente.</t>
   </si>
   <si>
-    <t>descripción</t>
-  </si>
-  <si>
-    <t>capacidadPersonas</t>
-  </si>
-  <si>
-    <t>tiempoUso</t>
-  </si>
-  <si>
-    <t>unidadTiempoUso</t>
-  </si>
-  <si>
     <t>Agenda turno Diurno</t>
   </si>
   <si>
@@ -356,9 +263,6 @@
     <t>NoDisponible</t>
   </si>
   <si>
-    <t>Objeto de dominio que representa a cada una de las zonas comúnes que tendrán una agenda y respectivos turnos.</t>
-  </si>
-  <si>
     <t>Objeto de dominio que representaa cada una de las agendas que dónde el residente podrá reservar.</t>
   </si>
   <si>
@@ -366,6 +270,81 @@
   </si>
   <si>
     <t>No es posible tener un nombre con la misma agenda para la misma hora de inicio y hora final  para una misma turno.</t>
+  </si>
+  <si>
+    <t>nombreZonaComun</t>
+  </si>
+  <si>
+    <t>capacidadPersonasZonaComun</t>
+  </si>
+  <si>
+    <t>identificadorConjuntoResidencial</t>
+  </si>
+  <si>
+    <t>nombreConjuntoResidencial</t>
+  </si>
+  <si>
+    <t>identificadorUnidadTiempoUso</t>
+  </si>
+  <si>
+    <t>nombreUnidadTiempoUso</t>
+  </si>
+  <si>
+    <t>abreviaturaUnidadTiempoUso</t>
+  </si>
+  <si>
+    <t>enBaseUnidadTiempoUso</t>
+  </si>
+  <si>
+    <t>IdentificadorZonaComun</t>
+  </si>
+  <si>
+    <t>decripcionZonaComun</t>
+  </si>
+  <si>
+    <t>tiempoUsoZonaComun</t>
+  </si>
+  <si>
+    <t>Forest apartamentos</t>
+  </si>
+  <si>
+    <t>Natural</t>
+  </si>
+  <si>
+    <t>Riogrande</t>
+  </si>
+  <si>
+    <t>Ventus</t>
+  </si>
+  <si>
+    <t>Minuto</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>True</t>
+  </si>
+  <si>
+    <t>Es un dato que hace que cada conjunto residencial sea único.</t>
+  </si>
+  <si>
+    <t>Es un dato que representa al nombre de un conjunto residencial</t>
+  </si>
+  <si>
+    <t>Es un dato que hace que cada unidad de tiempo de uso sea unica.</t>
+  </si>
+  <si>
+    <t>Es un dato que respresenta en texto como queda abreviada la unidad especifica.</t>
+  </si>
+  <si>
+    <t>Es un dato logico que reprenta que unidad esta activa para medir el tiempo de uso permitido para que un residente use una zona común.</t>
+  </si>
+  <si>
+    <t>Este es le dato que representa el tiempo de uso por numero entero positivo de un residente</t>
+  </si>
+  <si>
+    <t>Objeto de dominio que representa el contexto conjuntos residenciales que tendrán una agenda y respectivos turnos.</t>
   </si>
 </sst>
 </file>
@@ -557,7 +536,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
@@ -601,9 +580,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -622,80 +598,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -704,6 +606,99 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -727,58 +722,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Objetos de dominio"/>
-      <sheetName val="Administrador"/>
-      <sheetName val="ConjuntoResidencial"/>
-      <sheetName val="Zonainmueble"/>
-      <sheetName val="Inmueble"/>
-      <sheetName val="ZonaComun"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2">
-        <row r="4">
-          <cell r="I4" t="str">
-            <v>Forest apartamentos</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5" t="str">
-            <v>Natural</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6" t="str">
-            <v>Riogrande</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="I7" t="str">
-            <v>Bolivar</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="I8" t="str">
-            <v>Ventus</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1099,13 +1042,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ADC7617-6509-431F-A99E-8882BF74D5E4}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.6640625" customWidth="1"/>
-    <col min="2" max="2" width="58.33203125" customWidth="1"/>
+    <col min="1" max="1" width="27.7109375" customWidth="1"/>
+    <col min="2" max="2" width="58.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1113,28 +1056,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>5</v>
-      </c>
       <c r="B4" s="4" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1149,22 +1092,27 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AAB45A7-2401-4156-812B-1376902CA2CF}">
-  <dimension ref="A1:J15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.6640625" customWidth="1"/>
-    <col min="3" max="3" width="24.6640625" customWidth="1"/>
-    <col min="4" max="4" width="27" customWidth="1"/>
-    <col min="5" max="7" width="21.6640625" customWidth="1"/>
-    <col min="8" max="8" width="20.33203125" customWidth="1"/>
-    <col min="9" max="9" width="23.6640625" customWidth="1"/>
-    <col min="10" max="10" width="33.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.5546875" customWidth="1"/>
+    <col min="1" max="1" width="32.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="22" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -1175,48 +1123,56 @@
       <c r="H1" s="5"/>
       <c r="I1" s="5"/>
       <c r="J1" s="5"/>
-    </row>
-    <row r="2" spans="1:10" s="35" customFormat="1" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="34" t="s">
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+    </row>
+    <row r="2" spans="1:12" s="34" customFormat="1" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="43" t="s">
+        <v>95</v>
+      </c>
+      <c r="B2" s="43" t="s">
+        <v>96</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="F2" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="G2" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="34" t="s">
+      <c r="I2" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="34" t="s">
-        <v>69</v>
-      </c>
-      <c r="D2" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2" s="34" t="s">
+      <c r="K2" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="L2" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="34" t="s">
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G2" s="34" t="s">
+      <c r="C3" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="H2" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="I2" s="34" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" s="34" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>82</v>
@@ -1231,346 +1187,390 @@
         <v>85</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="J3" s="20" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="L3" s="20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="25">
         <v>1</v>
       </c>
       <c r="B4" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="26">
+        <v>2</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="G4" s="25">
+        <v>1</v>
+      </c>
+      <c r="H4" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="25">
+        <v>50</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" s="25">
+        <v>120</v>
+      </c>
+      <c r="L4" s="42" t="str">
+        <f>_xlfn.CONCAT(A4,B4,"-",C4,D4,E4,F4,"-",G4,H4,I4,J4,K4,)</f>
+        <v>1Forest apartamentos-2MinutominTrue-1Piscina50Es un espacio deportivo y lúdico120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="27">
+        <v>1</v>
+      </c>
+      <c r="B5" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" s="26">
+        <v>2</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="F5" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="G5" s="27">
+        <v>2</v>
+      </c>
+      <c r="H5" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="27">
+        <v>20</v>
+      </c>
+      <c r="J5" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="K5" s="27">
+        <v>120</v>
+      </c>
+      <c r="L5" s="42" t="str">
+        <f t="shared" ref="L5:L12" si="0">_xlfn.CONCAT(A5,B5,"-",C5,D5,E5,F5,"-",G5,H5,I5,J5,K5,)</f>
+        <v>1Forest apartamentos-2MinutominTrue-2Gimnasio20Espacio que cuenta con diferentes maquinas para la ejercitación120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="27">
+        <v>1</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="26">
+        <v>2</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="F6" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="G6" s="27">
+        <v>3</v>
+      </c>
+      <c r="H6" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" s="27">
+        <v>15</v>
+      </c>
+      <c r="J6" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="K6" s="27">
+        <v>60</v>
+      </c>
+      <c r="L6" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>1Forest apartamentos-2MinutominTrue-3piscinaAdultos15Es un espacio deportivo y lúdico60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>2</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" s="26">
+        <v>2</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="G7" s="27">
+        <v>4</v>
+      </c>
+      <c r="H7" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="27">
+        <v>100</v>
+      </c>
+      <c r="J7" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="K7" s="27">
+        <v>60</v>
+      </c>
+      <c r="L7" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>2Natural-2MinutominTrue-4Salón de Eventos100Un espacio amplio para celebrar reuniones sociales y familiares.60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" s="27">
+        <v>2</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" s="26">
+        <v>2</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="F8" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="G8" s="27">
+        <v>5</v>
+      </c>
+      <c r="H8" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" s="27">
+        <v>22</v>
+      </c>
+      <c r="J8" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="K8" s="27">
+        <v>60</v>
+      </c>
+      <c r="L8" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>2Natural-2MinutominTrue-5Cancha de Fútbol22Cancha de césped sintético para actividades deportivas en equipo.60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <v>3</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" s="26">
+        <v>2</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="F9" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="G9" s="27">
+        <v>6</v>
+      </c>
+      <c r="H9" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="I9" s="27">
+        <v>20</v>
+      </c>
+      <c r="J9" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="K9" s="27">
+        <v>120</v>
+      </c>
+      <c r="L9" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>3Riogrande-2MinutominTrue-6Piscina Pequeña20Piscina diseñada para niños, con profundidades seguras y vigilancia.120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <v>3</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10" s="26">
+        <v>2</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="G10" s="27">
+        <v>7</v>
+      </c>
+      <c r="H10" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="I10" s="27">
+        <v>15</v>
+      </c>
+      <c r="J10" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="25">
-        <v>50</v>
-      </c>
-      <c r="F4" s="25">
+      <c r="K10" s="27">
+        <v>120</v>
+      </c>
+      <c r="L10" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>3Riogrande-2MinutominTrue-7Zona BBQ15Área equipada con parrillas y mesas para realizar asados al aire libre.120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <v>3</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" s="26">
+        <v>2</v>
+      </c>
+      <c r="D11" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="F11" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="G11" s="27">
+        <v>8</v>
+      </c>
+      <c r="H11" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="I11" s="27">
+        <v>4</v>
+      </c>
+      <c r="J11" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="K11" s="27">
         <v>60</v>
       </c>
-      <c r="G4" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I4" s="26" t="str">
-        <f>[1]ConjuntoResidencial!$I$4</f>
-        <v>Forest apartamentos</v>
-      </c>
-      <c r="J4" s="27" t="str">
-        <f>_xlfn.CONCAT(B4,"-",I4)</f>
-        <v>Piscina-Forest apartamentos</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="28">
+      <c r="L11" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>3Riogrande-2MinutominTrue-8Cancha de Tenis4Espacio deportivo para la práctica de tenis en un ambiente profesional60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A12" s="27">
+        <v>5</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" s="26">
         <v>2</v>
       </c>
-      <c r="B5" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" s="29" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" s="28">
-        <v>20</v>
-      </c>
-      <c r="F5" s="28">
-        <v>120</v>
-      </c>
-      <c r="G5" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="H5" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="I5" s="26" t="str">
-        <f>[1]ConjuntoResidencial!$I$4</f>
-        <v>Forest apartamentos</v>
-      </c>
-      <c r="J5" s="27" t="str">
-        <f>_xlfn.CONCAT(B5,"-",I5)</f>
-        <v>Gimnasio-Forest apartamentos</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="28">
-        <v>3</v>
-      </c>
-      <c r="B6" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="28">
-        <v>15</v>
-      </c>
-      <c r="F6" s="28">
-        <v>1</v>
-      </c>
-      <c r="G6" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I6" s="26" t="str">
-        <f>[1]ConjuntoResidencial!$I$5</f>
-        <v>Natural</v>
-      </c>
-      <c r="J6" s="27" t="str">
-        <f>_xlfn.CONCAT(B6,"-",I6)</f>
-        <v>piscinaAdultos-Natural</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="28">
-        <v>4</v>
-      </c>
-      <c r="B7" s="28" t="s">
+      <c r="D12" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="F12" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="G12" s="27">
+        <v>9</v>
+      </c>
+      <c r="H12" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="I12" s="27">
+        <v>10</v>
+      </c>
+      <c r="J12" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="E7" s="28">
-        <v>100</v>
-      </c>
-      <c r="F7" s="28">
-        <v>4</v>
-      </c>
-      <c r="G7" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="H7" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="I7" s="26" t="str">
-        <f>[1]ConjuntoResidencial!I6</f>
-        <v>Riogrande</v>
-      </c>
-      <c r="J7" s="27" t="str">
-        <f t="shared" ref="J7:J12" si="0">_xlfn.CONCAT(B7,"-",I7)</f>
-        <v>Salón de Eventos-Riogrande</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="72" x14ac:dyDescent="0.3">
-      <c r="A8" s="28">
-        <v>5</v>
-      </c>
-      <c r="B8" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="29" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" s="28">
-        <v>22</v>
-      </c>
-      <c r="F8" s="28">
-        <v>90</v>
-      </c>
-      <c r="G8" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="I8" s="26" t="str">
-        <f>[1]ConjuntoResidencial!I7</f>
-        <v>Bolivar</v>
-      </c>
-      <c r="J8" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v>Cancha de Fútbol-Bolivar</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="72" x14ac:dyDescent="0.3">
-      <c r="A9" s="28">
-        <v>6</v>
-      </c>
-      <c r="B9" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="D9" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="E9" s="28">
-        <v>20</v>
-      </c>
-      <c r="F9" s="28">
-        <v>45</v>
-      </c>
-      <c r="G9" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="I9" s="26" t="str">
-        <f>[1]ConjuntoResidencial!I5</f>
-        <v>Natural</v>
-      </c>
-      <c r="J9" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v>Piscina Pequeña-Natural</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="28">
-        <v>7</v>
-      </c>
-      <c r="B10" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="D10" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="E10" s="28">
-        <v>15</v>
-      </c>
-      <c r="F10" s="28">
-        <v>2</v>
-      </c>
-      <c r="G10" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="H10" s="29" t="s">
+      <c r="K12" s="27">
         <v>60</v>
       </c>
-      <c r="I10" s="26" t="str">
-        <f>[1]ConjuntoResidencial!I8</f>
-        <v>Ventus</v>
-      </c>
-      <c r="J10" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v>Zona BBQ-Ventus</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="28">
-        <v>8</v>
-      </c>
-      <c r="B11" s="28" t="s">
-        <v>61</v>
-      </c>
-      <c r="C11" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="D11" s="29" t="s">
-        <v>63</v>
-      </c>
-      <c r="E11" s="28">
-        <v>4</v>
-      </c>
-      <c r="F11" s="28">
-        <v>60</v>
-      </c>
-      <c r="G11" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="H11" s="29" t="s">
-        <v>64</v>
-      </c>
-      <c r="I11" s="26" t="str">
-        <f>[1]ConjuntoResidencial!I6</f>
-        <v>Riogrande</v>
-      </c>
-      <c r="J11" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v>Cancha de Tenis-Riogrande</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="28">
-        <v>9</v>
-      </c>
-      <c r="B12" s="28" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="D12" s="29" t="s">
-        <v>67</v>
-      </c>
-      <c r="E12" s="28">
-        <v>10</v>
-      </c>
-      <c r="F12" s="28">
-        <v>90</v>
-      </c>
-      <c r="G12" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="H12" s="29" t="s">
-        <v>68</v>
-      </c>
-      <c r="I12" s="26" t="str">
-        <f>[1]ConjuntoResidencial!I4</f>
-        <v>Forest apartamentos</v>
-      </c>
-      <c r="J12" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v>Sala de Juegos-Forest apartamentos</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B13" s="30"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="32"/>
-      <c r="H13" s="32"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C14" s="31"/>
-      <c r="D14" s="32"/>
-      <c r="H14" s="32"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C15" s="31"/>
-      <c r="D15" s="32"/>
-      <c r="H15" s="32"/>
+      <c r="L12" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>5Ventus-2MinutominTrue-9Sala de Juegos10Sala equipada con mesas de ping-pong, billar y juegos de mesa para el disfrute familiar.60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B13" s="29"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="31"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C14" s="30"/>
+      <c r="D14" s="31"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C15" s="30"/>
+      <c r="D15" s="31"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de dominio'!A3" display="&lt;&lt;&lt;&lt;&lt;&lt; Volver al inicio" xr:uid="{A0AE4026-06D0-4B79-8276-3FD9B659C919}"/>
     <hyperlink ref="B1" location="Objetos de dominio!A1" display="Objetos de dominio!A1" xr:uid="{C619ADD0-FE27-4AF5-8B7C-7689D44C2683}"/>
-    <hyperlink ref="J1" location="Objetos de dominio!A1" display="Objetos de dominio!A1" xr:uid="{FF6BA809-A096-4F93-9F21-8FB482EBED8F}"/>
-    <hyperlink ref="I3" location="ConjuntoResidencial!A1" display="ConjuntoResidencial" xr:uid="{05C56B1E-409F-41D4-8EFB-8A54E79EAA73}"/>
-    <hyperlink ref="I4" location="ConjuntoResidencial!A5" display="ConjuntoResidencial!A5" xr:uid="{20734031-C260-43F4-8767-F3333840A51B}"/>
-    <hyperlink ref="I5" location="ConjuntoResidencial!A5" display="ConjuntoResidencial!A5" xr:uid="{FE96774E-A8E6-4221-865A-F02139CB51AB}"/>
-    <hyperlink ref="I6" location="ConjuntoResidencial!A5" display="ConjuntoResidencial!A5" xr:uid="{8C2C4EF3-9441-4B8C-A3BD-56176FF26603}"/>
+    <hyperlink ref="L1" location="Objetos de dominio!A1" display="Objetos de dominio!A1" xr:uid="{FF6BA809-A096-4F93-9F21-8FB482EBED8F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1579,324 +1579,325 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4578BD62-C112-42DC-9A20-08C85087F0AF}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="40.44140625" customWidth="1"/>
-    <col min="3" max="3" width="40.5546875" customWidth="1"/>
-    <col min="4" max="4" width="17.33203125" customWidth="1"/>
-    <col min="5" max="5" width="46.109375" customWidth="1"/>
-    <col min="6" max="6" width="44.6640625" customWidth="1"/>
-    <col min="7" max="7" width="98.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="40.42578125" customWidth="1"/>
+    <col min="3" max="3" width="40.5703125" customWidth="1"/>
+    <col min="4" max="4" width="17.28515625" customWidth="1"/>
+    <col min="5" max="5" width="46.140625" customWidth="1"/>
+    <col min="6" max="6" width="44.7109375" customWidth="1"/>
+    <col min="7" max="7" width="98.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="68" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="41" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="5"/>
+    </row>
+    <row r="2" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="5"/>
-    </row>
-    <row r="2" spans="1:7" ht="69" x14ac:dyDescent="0.3">
-      <c r="A2" s="34" t="s">
+      <c r="B2" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="34" t="s">
+      <c r="C2" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" s="33" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="D2" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="E2" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="F2" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="G2" s="34" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="D3" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="46" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="47">
+        <v>1</v>
+      </c>
+      <c r="B4" s="48" t="str">
+        <f>ZonaComun!L4</f>
+        <v>1Forest apartamentos-2MinutominTrue-1Piscina50Es un espacio deportivo y lúdico120</v>
+      </c>
+      <c r="C4" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="49">
+        <v>45553.25</v>
+      </c>
+      <c r="F4" s="49">
+        <v>45553.583333333336</v>
+      </c>
+      <c r="G4" s="46" t="str">
+        <f>B4&amp;" "&amp;TEXT(E4,"- dd  mmmm yyyy h:mm:ss AM/PM ")&amp;" hasta "&amp;TEXT(F4,"- dd  mmmm yyyy h:mm:ss AM/PM ")</f>
+        <v xml:space="preserve">1Forest apartamentos-2MinutominTrue-1Piscina50Es un espacio deportivo y lúdico120 - 18  septiembre 2024 6:00:00 a. m.  hasta - 18  septiembre 2024 2:00:00 p. m. </v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="47">
+        <v>2</v>
+      </c>
+      <c r="B5" s="48" t="str">
+        <f>ZonaComun!L4</f>
+        <v>1Forest apartamentos-2MinutominTrue-1Piscina50Es un espacio deportivo y lúdico120</v>
+      </c>
+      <c r="C5" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="49">
+        <v>45553.625</v>
+      </c>
+      <c r="F5" s="49">
+        <v>45553.875</v>
+      </c>
+      <c r="G5" s="46" t="str">
+        <f t="shared" ref="G5:G13" si="0">B5&amp;" "&amp;TEXT(E5,"- dd  mmmm yyyy h:mm:ss AM/PM ")&amp;" hasta "&amp;TEXT(F5,"- dd  mmmm yyyy h:mm:ss AM/PM ")</f>
+        <v xml:space="preserve">1Forest apartamentos-2MinutominTrue-1Piscina50Es un espacio deportivo y lúdico120 - 18  septiembre 2024 3:00:00 p. m.  hasta - 18  septiembre 2024 9:00:00 p. m. </v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="50">
         <v>3</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="B6" s="51" t="str">
+        <f>ZonaComun!L5</f>
+        <v>1Forest apartamentos-2MinutominTrue-2Gimnasio20Espacio que cuenta con diferentes maquinas para la ejercitación120</v>
+      </c>
+      <c r="C6" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="50" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="52">
+        <v>45553.25</v>
+      </c>
+      <c r="F6" s="52">
+        <v>45553.583333333336</v>
+      </c>
+      <c r="G6" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">1Forest apartamentos-2MinutominTrue-2Gimnasio20Espacio que cuenta con diferentes maquinas para la ejercitación120 - 18  septiembre 2024 6:00:00 a. m.  hasta - 18  septiembre 2024 2:00:00 p. m. </v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="50">
+        <v>4</v>
+      </c>
+      <c r="B7" s="51" t="str">
+        <f>ZonaComun!L5</f>
+        <v>1Forest apartamentos-2MinutominTrue-2Gimnasio20Espacio que cuenta con diferentes maquinas para la ejercitación120</v>
+      </c>
+      <c r="C7" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="50" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="52">
+        <v>45553.625</v>
+      </c>
+      <c r="F7" s="52">
+        <v>45553.875</v>
+      </c>
+      <c r="G7" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">1Forest apartamentos-2MinutominTrue-2Gimnasio20Espacio que cuenta con diferentes maquinas para la ejercitación120 - 18  septiembre 2024 3:00:00 p. m.  hasta - 18  septiembre 2024 9:00:00 p. m. </v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="53">
+        <v>5</v>
+      </c>
+      <c r="B8" s="54" t="str">
+        <f>ZonaComun!L6</f>
+        <v>1Forest apartamentos-2MinutominTrue-3piscinaAdultos15Es un espacio deportivo y lúdico60</v>
+      </c>
+      <c r="C8" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="55">
+        <v>45555.416666666664</v>
+      </c>
+      <c r="F8" s="55">
+        <v>45555.541666666664</v>
+      </c>
+      <c r="G8" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">1Forest apartamentos-2MinutominTrue-3piscinaAdultos15Es un espacio deportivo y lúdico60 - 20  septiembre 2024 10:00:00 a. m.  hasta - 20  septiembre 2024 1:00:00 p. m. </v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="56">
+        <v>6</v>
+      </c>
+      <c r="B9" s="57" t="str">
+        <f>ZonaComun!L7</f>
+        <v>2Natural-2MinutominTrue-4Salón de Eventos100Un espacio amplio para celebrar reuniones sociales y familiares.60</v>
+      </c>
+      <c r="C9" s="56" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" s="56" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" s="58">
+        <v>45553.333333333336</v>
+      </c>
+      <c r="F9" s="58">
+        <v>45553.5</v>
+      </c>
+      <c r="G9" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">2Natural-2MinutominTrue-4Salón de Eventos100Un espacio amplio para celebrar reuniones sociales y familiares.60 - 18  septiembre 2024 8:00:00 a. m.  hasta - 18  septiembre 2024 12:00:00 p. m. </v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="59">
+        <v>7</v>
+      </c>
+      <c r="B10" s="60" t="str">
+        <f>ZonaComun!L8</f>
+        <v>2Natural-2MinutominTrue-5Cancha de Fútbol22Cancha de césped sintético para actividades deportivas en equipo.60</v>
+      </c>
+      <c r="C10" s="59" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="59" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="61">
+        <v>45553.333333333336</v>
+      </c>
+      <c r="F10" s="61">
+        <v>45553.5</v>
+      </c>
+      <c r="G10" s="46" t="str">
+        <f>B10&amp;" "&amp;TEXT(E10,"- dd  mmmm yyyy h:mm:ss AM/PM ")&amp;" hasta "&amp;TEXT(F10,"- dd  mmmm yyyy h:mm:ss AM/PM ")</f>
+        <v xml:space="preserve">2Natural-2MinutominTrue-5Cancha de Fútbol22Cancha de césped sintético para actividades deportivas en equipo.60 - 18  septiembre 2024 8:00:00 a. m.  hasta - 18  septiembre 2024 12:00:00 p. m. </v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="62">
+        <v>8</v>
+      </c>
+      <c r="B11" s="63" t="str">
+        <f>ZonaComun!L9</f>
+        <v>3Riogrande-2MinutominTrue-6Piscina Pequeña20Piscina diseñada para niños, con profundidades seguras y vigilancia.120</v>
+      </c>
+      <c r="C11" s="62" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" s="62" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="64">
+        <v>45555.333333333336</v>
+      </c>
+      <c r="F11" s="64">
+        <v>45555.5</v>
+      </c>
+      <c r="G11" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">3Riogrande-2MinutominTrue-6Piscina Pequeña20Piscina diseñada para niños, con profundidades seguras y vigilancia.120 - 20  septiembre 2024 8:00:00 a. m.  hasta - 20  septiembre 2024 12:00:00 p. m. </v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" s="65">
+        <v>9</v>
+      </c>
+      <c r="B12" s="66" t="str">
+        <f>ZonaComun!L10</f>
+        <v>3Riogrande-2MinutominTrue-7Zona BBQ15Área equipada con parrillas y mesas para realizar asados al aire libre.120</v>
+      </c>
+      <c r="C12" s="67" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="65" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="68">
+        <v>45555.333333333336</v>
+      </c>
+      <c r="F12" s="68">
+        <v>45555.5</v>
+      </c>
+      <c r="G12" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">3Riogrande-2MinutominTrue-7Zona BBQ15Área equipada con parrillas y mesas para realizar asados al aire libre.120 - 20  septiembre 2024 8:00:00 a. m.  hasta - 20  septiembre 2024 12:00:00 p. m. </v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="69">
         <v>10</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="6" t="s">
+      <c r="B13" s="70" t="str">
+        <f>ZonaComun!L11</f>
+        <v>3Riogrande-2MinutominTrue-8Cancha de Tenis4Espacio deportivo para la práctica de tenis en un ambiente profesional60</v>
+      </c>
+      <c r="C13" s="71" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="69" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="36">
-        <v>1</v>
-      </c>
-      <c r="B4" s="37" t="str">
-        <f>ZonaComun!J4</f>
-        <v>Piscina-Forest apartamentos</v>
-      </c>
-      <c r="C4" s="36" t="s">
-        <v>86</v>
-      </c>
-      <c r="D4" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="38">
-        <v>45553.25</v>
-      </c>
-      <c r="F4" s="38">
-        <v>45553.583333333336</v>
-      </c>
-      <c r="G4" s="6" t="str">
-        <f>B4&amp;" "&amp;TEXT(E4,"- dd  mmmm yyyy h:mm:ss AM/PM ")&amp;" hasta "&amp;TEXT(F4,"- dd  mmmm yyyy h:mm:ss AM/PM ")</f>
-        <v xml:space="preserve">Piscina-Forest apartamentos - 18  septiembre 2024 6:00:00 a. m.  hasta - 18  septiembre 2024 2:00:00 p. m. </v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="36">
-        <v>2</v>
-      </c>
-      <c r="B5" s="37" t="str">
-        <f>ZonaComun!J4</f>
-        <v>Piscina-Forest apartamentos</v>
-      </c>
-      <c r="C5" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="D5" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="38">
-        <v>45553.625</v>
-      </c>
-      <c r="F5" s="38">
-        <v>45553.875</v>
-      </c>
-      <c r="G5" s="6" t="str">
-        <f t="shared" ref="G5:G13" si="0">B5&amp;" "&amp;TEXT(E5,"- dd  mmmm yyyy h:mm:ss AM/PM ")&amp;" hasta "&amp;TEXT(F5,"- dd  mmmm yyyy h:mm:ss AM/PM ")</f>
-        <v xml:space="preserve">Piscina-Forest apartamentos - 18  septiembre 2024 3:00:00 p. m.  hasta - 18  septiembre 2024 9:00:00 p. m. </v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="39">
-        <v>3</v>
-      </c>
-      <c r="B6" s="40" t="str">
-        <f>ZonaComun!J5</f>
-        <v>Gimnasio-Forest apartamentos</v>
-      </c>
-      <c r="C6" s="39" t="s">
-        <v>86</v>
-      </c>
-      <c r="D6" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="41">
-        <v>45553.25</v>
-      </c>
-      <c r="F6" s="41">
-        <v>45553.583333333336</v>
-      </c>
-      <c r="G6" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">Gimnasio-Forest apartamentos - 18  septiembre 2024 6:00:00 a. m.  hasta - 18  septiembre 2024 2:00:00 p. m. </v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="39">
-        <v>4</v>
-      </c>
-      <c r="B7" s="40" t="str">
-        <f>ZonaComun!J5</f>
-        <v>Gimnasio-Forest apartamentos</v>
-      </c>
-      <c r="C7" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="D7" s="39" t="s">
-        <v>94</v>
-      </c>
-      <c r="E7" s="41">
-        <v>45553.625</v>
-      </c>
-      <c r="F7" s="41">
-        <v>45553.875</v>
-      </c>
-      <c r="G7" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">Gimnasio-Forest apartamentos - 18  septiembre 2024 3:00:00 p. m.  hasta - 18  septiembre 2024 9:00:00 p. m. </v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="42">
-        <v>5</v>
-      </c>
-      <c r="B8" s="43" t="str">
-        <f>ZonaComun!J6</f>
-        <v>piscinaAdultos-Natural</v>
-      </c>
-      <c r="C8" s="42" t="s">
-        <v>88</v>
-      </c>
-      <c r="D8" s="42" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="44">
-        <v>45555.416666666664</v>
-      </c>
-      <c r="F8" s="44">
-        <v>45555.541666666664</v>
-      </c>
-      <c r="G8" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">piscinaAdultos-Natural - 20  septiembre 2024 10:00:00 a. m.  hasta - 20  septiembre 2024 1:00:00 p. m. </v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="45">
-        <v>6</v>
-      </c>
-      <c r="B9" s="46" t="str">
-        <f>ZonaComun!J7</f>
-        <v>Salón de Eventos-Riogrande</v>
-      </c>
-      <c r="C9" s="45" t="s">
-        <v>89</v>
-      </c>
-      <c r="D9" s="45" t="s">
-        <v>94</v>
-      </c>
-      <c r="E9" s="47">
-        <v>45553.333333333336</v>
-      </c>
-      <c r="F9" s="47">
-        <v>45553.5</v>
-      </c>
-      <c r="G9" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">Salón de Eventos-Riogrande - 18  septiembre 2024 8:00:00 a. m.  hasta - 18  septiembre 2024 12:00:00 p. m. </v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="48">
-        <v>7</v>
-      </c>
-      <c r="B10" s="49" t="str">
-        <f>ZonaComun!J8</f>
-        <v>Cancha de Fútbol-Bolivar</v>
-      </c>
-      <c r="C10" s="48" t="s">
-        <v>90</v>
-      </c>
-      <c r="D10" s="48" t="s">
-        <v>94</v>
-      </c>
-      <c r="E10" s="50">
-        <v>45553.333333333336</v>
-      </c>
-      <c r="F10" s="50">
-        <v>45553.5</v>
-      </c>
-      <c r="G10" s="6" t="str">
-        <f>B10&amp;" "&amp;TEXT(E10,"- dd  mmmm yyyy h:mm:ss AM/PM ")&amp;" hasta "&amp;TEXT(F10,"- dd  mmmm yyyy h:mm:ss AM/PM ")</f>
-        <v xml:space="preserve">Cancha de Fútbol-Bolivar - 18  septiembre 2024 8:00:00 a. m.  hasta - 18  septiembre 2024 12:00:00 p. m. </v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="51">
-        <v>8</v>
-      </c>
-      <c r="B11" s="52" t="str">
-        <f>ZonaComun!J9</f>
-        <v>Piscina Pequeña-Natural</v>
-      </c>
-      <c r="C11" s="51" t="s">
-        <v>91</v>
-      </c>
-      <c r="D11" s="51" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="53">
-        <v>45555.333333333336</v>
-      </c>
-      <c r="F11" s="53">
-        <v>45555.5</v>
-      </c>
-      <c r="G11" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">Piscina Pequeña-Natural - 20  septiembre 2024 8:00:00 a. m.  hasta - 20  septiembre 2024 12:00:00 p. m. </v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="54">
-        <v>9</v>
-      </c>
-      <c r="B12" s="55" t="str">
-        <f>ZonaComun!J10</f>
-        <v>Zona BBQ-Ventus</v>
-      </c>
-      <c r="C12" s="56" t="s">
-        <v>92</v>
-      </c>
-      <c r="D12" s="54" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" s="57">
-        <v>45555.333333333336</v>
-      </c>
-      <c r="F12" s="57">
-        <v>45555.5</v>
-      </c>
-      <c r="G12" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">Zona BBQ-Ventus - 20  septiembre 2024 8:00:00 a. m.  hasta - 20  septiembre 2024 12:00:00 p. m. </v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="58">
-        <v>10</v>
-      </c>
-      <c r="B13" s="59" t="str">
-        <f>ZonaComun!J11</f>
-        <v>Cancha de Tenis-Riogrande</v>
-      </c>
-      <c r="C13" s="60" t="s">
-        <v>93</v>
-      </c>
-      <c r="D13" s="58" t="s">
-        <v>15</v>
-      </c>
-      <c r="E13" s="61">
+      <c r="E13" s="72">
         <v>45557.333333333336</v>
       </c>
-      <c r="F13" s="61">
+      <c r="F13" s="72">
         <v>45557.5</v>
       </c>
-      <c r="G13" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">Cancha de Tenis-Riogrande - 22  septiembre 2024 8:00:00 a. m.  hasta - 22  septiembre 2024 12:00:00 p. m. </v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="33"/>
+      <c r="G13" s="46" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">3Riogrande-2MinutominTrue-8Cancha de Tenis4Espacio deportivo para la práctica de tenis en un ambiente profesional60 - 22  septiembre 2024 8:00:00 a. m.  hasta - 22  septiembre 2024 12:00:00 p. m. </v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1923,78 +1924,78 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1481DBD8-8614-460B-A4B3-0BC96282F835}">
   <dimension ref="A1:G30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.109375" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" customWidth="1"/>
-    <col min="6" max="6" width="133.6640625" customWidth="1"/>
-    <col min="7" max="7" width="140.6640625" customWidth="1"/>
+    <col min="3" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="133.7109375" customWidth="1"/>
+    <col min="7" max="7" width="140.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="68" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="41" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
       <c r="F1" s="5"/>
     </row>
-    <row r="2" spans="1:7" ht="96.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="34" t="s">
+    <row r="2" spans="1:7" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="C2" s="34" t="s">
+      <c r="D2" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="34" t="s">
-        <v>75</v>
-      </c>
-      <c r="F2" s="34" t="s">
+      <c r="E2" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="G2" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="G2" s="34" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4" s="8">
         <v>0.25</v>
@@ -2003,22 +2004,22 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="G4" s="10" t="str">
         <f>_xlfn.CONCAT(B4,"-",F4,"-",TEXT(C4," h:mm:ss AM/PM "),"-",TEXT(D4," h:mm:ss AM/PM "))</f>
         <v xml:space="preserve">Turno 1-Piscina-Forest apartamentos - 18  septiembre 2024 6:00:00 a. m.  hasta - 18  septiembre 2024 2:00:00 p. m. - 6:00:00 a. m. - 8:00:00 a. m. </v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C5" s="8">
         <v>0.33333333333333331</v>
@@ -2027,22 +2028,22 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="G5" s="10" t="str">
         <f t="shared" ref="G5:G21" si="0">_xlfn.CONCAT(B5,"-",F5,"-",TEXT(C5," h:mm:ss AM/PM "),"-",TEXT(D5," h:mm:ss AM/PM "))</f>
         <v xml:space="preserve">Turno 2-Piscina-Forest apartamentos - 18  septiembre 2024 6:00:00 a. m.  hasta - 18  septiembre 2024 2:00:00 p. m. - 8:00:00 a. m. - 10:00:00 a. m. </v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" s="8">
         <v>0.41666666666666669</v>
@@ -2051,22 +2052,22 @@
         <v>0.5</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="G6" s="10" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">Turno 3-Piscina-Forest apartamentos - 18  septiembre 2024 6:00:00 a. m.  hasta - 18  septiembre 2024 2:00:00 p. m. - 10:00:00 a. m. - 12:00:00 p. m. </v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7" s="8">
         <v>0.54166666666666696</v>
@@ -2075,22 +2076,22 @@
         <v>0.58333333333333404</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="G7" s="10" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">Turno 4-Piscina-Forest apartamentos - 18  septiembre 2024 6:00:00 a. m.  hasta - 18  septiembre 2024 2:00:00 p. m. - 1:00:00 p. m. - 2:00:00 p. m. </v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>5</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" s="12">
         <v>0.625</v>
@@ -2099,22 +2100,22 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="G8" s="10" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">Turno 1-Gimnasio-Forest apartamentos - 18  septiembre 2024 3:00:00 p. m.  hasta - 18  septiembre 2024 9:00:00 p. m. - 3:00:00 p. m. - 5:00:00 p. m. </v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>6</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9" s="12">
         <v>0.70833333333333337</v>
@@ -2123,22 +2124,22 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="G9" s="10" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">Turno 2-Gimnasio-Forest apartamentos - 18  septiembre 2024 3:00:00 p. m.  hasta - 18  septiembre 2024 9:00:00 p. m. - 5:00:00 p. m. - 7:00:00 p. m. </v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>7</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C10" s="12">
         <v>0.79166666666666663</v>
@@ -2147,22 +2148,22 @@
         <v>0.875</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="G10" s="10" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">Turno 3-Gimnasio-Forest apartamentos - 18  septiembre 2024 3:00:00 p. m.  hasta - 18  septiembre 2024 9:00:00 p. m. - 7:00:00 p. m. - 9:00:00 p. m. </v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
         <v>8</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C11" s="15">
         <v>0.91666666666666663</v>
@@ -2171,22 +2172,22 @@
         <v>0.95833333333333337</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F11" s="23" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="G11" s="10" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">Turno 1-piscinaAdultos-Natural - 20  septiembre 2024 10:00:00 a. m.  hasta - 20  septiembre 2024 1:00:00 p. m. - 10:00:00 p. m. - 11:00:00 p. m. </v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="14">
         <v>9</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C12" s="15">
         <v>0.45833333333333331</v>
@@ -2195,22 +2196,22 @@
         <v>0.5</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F12" s="23" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="G12" s="10" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">Turno 2-piscinaAdultos-Natural - 20  septiembre 2024 10:00:00 a. m.  hasta - 20  septiembre 2024 1:00:00 p. m. - 11:00:00 a. m. - 12:00:00 p. m. </v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
         <v>10</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C13" s="15">
         <v>0.5</v>
@@ -2219,22 +2220,22 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F13" s="23" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="G13" s="10" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">Turno 3-piscinaAdultos-Natural - 20  septiembre 2024 10:00:00 a. m.  hasta - 20  septiembre 2024 1:00:00 p. m. - 12:00:00 p. m. - 1:00:00 p. m. </v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="17">
         <v>11</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C14" s="18">
         <v>0.33333333333333331</v>
@@ -2243,22 +2244,22 @@
         <v>0.375</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="G14" s="10" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">Turno 1-Salón de Eventos-Riogrande - 18  septiembre 2024 8:00:00 a. m.  hasta - 18  septiembre 2024 12:00:00 p. m. - 8:00:00 a. m. - 9:00:00 a. m. </v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="17">
         <v>12</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="18">
         <v>0.375</v>
@@ -2267,22 +2268,22 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F15" s="24" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="G15" s="10" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">Turno 2-Salón de Eventos-Riogrande - 18  septiembre 2024 8:00:00 a. m.  hasta - 18  septiembre 2024 12:00:00 p. m. - 9:00:00 a. m. - 10:00:00 a. m. </v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="17">
         <v>13</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="18">
         <v>0.41666666666666702</v>
@@ -2291,22 +2292,22 @@
         <v>0.45833333333333398</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F16" s="24" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="G16" s="10" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">Turno 3-Salón de Eventos-Riogrande - 18  septiembre 2024 8:00:00 a. m.  hasta - 18  septiembre 2024 12:00:00 p. m. - 10:00:00 a. m. - 11:00:00 a. m. </v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="17">
         <v>14</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" s="18">
         <v>0.45833333333333398</v>
@@ -2315,211 +2316,211 @@
         <v>0.500000000000001</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F17" s="24" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="G17" s="10" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">Turno 4-Salón de Eventos-Riogrande - 18  septiembre 2024 8:00:00 a. m.  hasta - 18  septiembre 2024 12:00:00 p. m. - 11:00:00 a. m. - 12:00:00 p. m. </v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="65">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="38">
         <v>15</v>
       </c>
-      <c r="B18" s="66" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" s="66">
+      <c r="B18" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="39">
         <v>0.33333333333333331</v>
       </c>
-      <c r="D18" s="66">
+      <c r="D18" s="39">
         <v>0.375</v>
       </c>
-      <c r="E18" s="67" t="s">
-        <v>103</v>
-      </c>
-      <c r="F18" s="66" t="s">
-        <v>98</v>
+      <c r="E18" s="40" t="s">
+        <v>73</v>
+      </c>
+      <c r="F18" s="39" t="s">
+        <v>68</v>
       </c>
       <c r="G18" s="10" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">Turno 1-Cancha de Fútbol-Bolivar - 18  septiembre 2024 8:00:00 a. m.  hasta - 18  septiembre 2024 12:00:00 p. m. - 8:00:00 a. m. - 9:00:00 a. m. </v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="65">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="38">
         <v>16</v>
       </c>
-      <c r="B19" s="66" t="s">
+      <c r="B19" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="39">
+        <v>0.375</v>
+      </c>
+      <c r="D19" s="39">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="E19" s="40" t="s">
+        <v>73</v>
+      </c>
+      <c r="F19" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="G19" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Turno 2-Cancha de Fútbol-Bolivar - 18  septiembre 2024 8:00:00 a. m.  hasta - 18  septiembre 2024 12:00:00 p. m. - 9:00:00 a. m. - 10:00:00 a. m. </v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="38">
+        <v>17</v>
+      </c>
+      <c r="B20" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="66">
-        <v>0.375</v>
-      </c>
-      <c r="D19" s="66">
+      <c r="C20" s="39">
         <v>0.41666666666666702</v>
       </c>
-      <c r="E19" s="67" t="s">
-        <v>103</v>
-      </c>
-      <c r="F19" s="66" t="s">
-        <v>98</v>
-      </c>
-      <c r="G19" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">Turno 2-Cancha de Fútbol-Bolivar - 18  septiembre 2024 8:00:00 a. m.  hasta - 18  septiembre 2024 12:00:00 p. m. - 9:00:00 a. m. - 10:00:00 a. m. </v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="65">
-        <v>17</v>
-      </c>
-      <c r="B20" s="66" t="s">
+      <c r="D20" s="39">
+        <v>0.45833333333333398</v>
+      </c>
+      <c r="E20" s="40" t="s">
+        <v>73</v>
+      </c>
+      <c r="F20" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="G20" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Turno 3-Cancha de Fútbol-Bolivar - 18  septiembre 2024 8:00:00 a. m.  hasta - 18  septiembre 2024 12:00:00 p. m. - 10:00:00 a. m. - 11:00:00 a. m. </v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="38">
+        <v>18</v>
+      </c>
+      <c r="B21" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="66">
-        <v>0.41666666666666702</v>
-      </c>
-      <c r="D20" s="66">
+      <c r="C21" s="39">
         <v>0.45833333333333398</v>
       </c>
-      <c r="E20" s="67" t="s">
-        <v>103</v>
-      </c>
-      <c r="F20" s="66" t="s">
-        <v>98</v>
-      </c>
-      <c r="G20" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">Turno 3-Cancha de Fútbol-Bolivar - 18  septiembre 2024 8:00:00 a. m.  hasta - 18  septiembre 2024 12:00:00 p. m. - 10:00:00 a. m. - 11:00:00 a. m. </v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="65">
-        <v>18</v>
-      </c>
-      <c r="B21" s="66" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="66">
-        <v>0.45833333333333398</v>
-      </c>
-      <c r="D21" s="66">
+      <c r="D21" s="39">
         <v>0.500000000000001</v>
       </c>
-      <c r="E21" s="67" t="s">
-        <v>103</v>
-      </c>
-      <c r="F21" s="66" t="s">
-        <v>98</v>
+      <c r="E21" s="40" t="s">
+        <v>73</v>
+      </c>
+      <c r="F21" s="39" t="s">
+        <v>68</v>
       </c>
       <c r="G21" s="10" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">Turno 4-Cancha de Fútbol-Bolivar - 18  septiembre 2024 8:00:00 a. m.  hasta - 18  septiembre 2024 12:00:00 p. m. - 11:00:00 a. m. - 12:00:00 p. m. </v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="17">
         <v>19</v>
       </c>
-      <c r="B22" s="64"/>
-      <c r="C22" s="64"/>
-      <c r="D22" s="64"/>
-      <c r="E22" s="64"/>
-      <c r="F22" s="64"/>
-      <c r="G22" s="63" t="str">
+      <c r="B22" s="37"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="36" t="str">
         <f t="shared" ref="G22:G27" si="1">_xlfn.CONCAT(B22,"-",F22)</f>
         <v>-</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="17">
         <v>20</v>
       </c>
-      <c r="B23" s="64"/>
-      <c r="C23" s="64"/>
-      <c r="D23" s="64"/>
-      <c r="E23" s="64"/>
-      <c r="F23" s="64"/>
-      <c r="G23" s="63" t="str">
+      <c r="B23" s="37"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="36" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="17">
         <v>21</v>
       </c>
-      <c r="B24" s="64"/>
-      <c r="C24" s="64"/>
-      <c r="D24" s="64"/>
-      <c r="E24" s="64"/>
-      <c r="F24" s="64"/>
-      <c r="G24" s="63" t="str">
+      <c r="B24" s="37"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="36" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="17">
         <v>22</v>
       </c>
-      <c r="B25" s="64"/>
-      <c r="C25" s="64"/>
-      <c r="D25" s="64"/>
-      <c r="E25" s="64"/>
-      <c r="F25" s="64"/>
-      <c r="G25" s="63" t="str">
+      <c r="B25" s="37"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="36" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="17">
         <v>23</v>
       </c>
-      <c r="B26" s="64"/>
-      <c r="C26" s="64"/>
-      <c r="D26" s="64"/>
-      <c r="E26" s="64"/>
-      <c r="F26" s="64"/>
-      <c r="G26" s="63" t="str">
+      <c r="B26" s="37"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="36" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="17">
         <v>24</v>
       </c>
-      <c r="B27" s="64"/>
-      <c r="C27" s="64"/>
-      <c r="D27" s="64"/>
-      <c r="E27" s="64"/>
-      <c r="F27" s="64"/>
-      <c r="G27" s="63" t="str">
+      <c r="B27" s="37"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="36" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="17">
         <v>25</v>
       </c>
-      <c r="B28" s="64"/>
-      <c r="C28" s="64"/>
-      <c r="D28" s="64"/>
-      <c r="E28" s="64"/>
-      <c r="F28" s="64"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F29" s="62"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F30" s="62"/>
+      <c r="B28" s="37"/>
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F29" s="35"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F30" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="1">
